--- a/XC.xlsx
+++ b/XC.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393D0E5C-0B87-4278-9FD0-2B1EE3341ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F41EF9-721A-48D7-8AF3-FF199237126A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="2508" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="20448" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="48">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -152,96 +152,6 @@
   </si>
   <si>
     <t>洛杉矶</t>
-  </si>
-  <si>
-    <t>夏威夷</t>
-  </si>
-  <si>
-    <t>泰国</t>
-  </si>
-  <si>
-    <t>中国港澳台</t>
-  </si>
-  <si>
-    <t>日本</t>
-  </si>
-  <si>
-    <t>马来西亚</t>
-  </si>
-  <si>
-    <t>韩国</t>
-  </si>
-  <si>
-    <t>英国</t>
-  </si>
-  <si>
-    <t>美国</t>
-  </si>
-  <si>
-    <t>澳大利亚</t>
-  </si>
-  <si>
-    <t>卡塔尔</t>
-  </si>
-  <si>
-    <t>德国</t>
-  </si>
-  <si>
-    <t>阿联酋</t>
-  </si>
-  <si>
-    <t>意大利</t>
-  </si>
-  <si>
-    <t>法国</t>
-  </si>
-  <si>
-    <t>越南</t>
-  </si>
-  <si>
-    <t>葡萄牙</t>
-  </si>
-  <si>
-    <t>菲律宾</t>
-  </si>
-  <si>
-    <t>俄罗斯</t>
-  </si>
-  <si>
-    <t>荷兰</t>
-  </si>
-  <si>
-    <t>土耳其</t>
-  </si>
-  <si>
-    <t>加拿大</t>
-  </si>
-  <si>
-    <t>埃及</t>
-  </si>
-  <si>
-    <t>印度尼西亚</t>
-  </si>
-  <si>
-    <t>西班牙</t>
-  </si>
-  <si>
-    <t>塞尔维亚</t>
-  </si>
-  <si>
-    <t>柬埔寨</t>
-  </si>
-  <si>
-    <t>墨西哥</t>
-  </si>
-  <si>
-    <t>马尔代夫</t>
-  </si>
-  <si>
-    <t>冰岛</t>
-  </si>
-  <si>
-    <t>希腊</t>
   </si>
   <si>
     <t>出发日期</t>
@@ -269,7 +179,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="182" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -335,7 +245,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -346,13 +256,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
@@ -641,8 +548,8 @@
     <col min="4" max="4" width="19.77734375" customWidth="1"/>
     <col min="5" max="5" width="20.88671875" customWidth="1"/>
     <col min="6" max="6" width="41.109375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="4"/>
+    <col min="7" max="7" width="14.33203125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -656,19 +563,19 @@
         <v>22</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>76</v>
+        <v>44</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -681,7 +588,7 @@
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="4">
         <v>44912</v>
       </c>
       <c r="E2">
@@ -690,10 +597,10 @@
       <c r="F2" s="5">
         <v>1</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="5">
         <v>0</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="5">
         <v>0</v>
       </c>
     </row>
@@ -707,7 +614,7 @@
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>44913</v>
       </c>
       <c r="E3">
@@ -716,10 +623,10 @@
       <c r="F3" s="5">
         <v>2</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="5">
         <v>1</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="5">
         <v>1</v>
       </c>
     </row>
@@ -733,7 +640,7 @@
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <v>44914</v>
       </c>
       <c r="E4">
@@ -742,10 +649,10 @@
       <c r="F4" s="5">
         <v>3</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>2</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="5">
         <v>2</v>
       </c>
     </row>
@@ -759,7 +666,7 @@
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>44915</v>
       </c>
       <c r="E5">
@@ -768,10 +675,10 @@
       <c r="F5" s="5">
         <v>4</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <v>3</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="5">
         <v>3</v>
       </c>
     </row>
@@ -785,7 +692,7 @@
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>44916</v>
       </c>
       <c r="E6">
@@ -794,10 +701,10 @@
       <c r="F6" s="5">
         <v>5</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>4</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="5">
         <v>4</v>
       </c>
     </row>
@@ -811,7 +718,7 @@
       <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>44917</v>
       </c>
       <c r="E7">
@@ -820,10 +727,10 @@
       <c r="F7" s="5">
         <v>6</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="5">
         <v>5</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="5">
         <v>5</v>
       </c>
     </row>
@@ -837,7 +744,7 @@
       <c r="C8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>44918</v>
       </c>
       <c r="E8">
@@ -846,7 +753,7 @@
       <c r="F8" s="5">
         <v>7</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <v>6</v>
       </c>
     </row>
@@ -860,7 +767,7 @@
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>44919</v>
       </c>
       <c r="E9">
@@ -880,7 +787,7 @@
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
         <v>44920</v>
       </c>
       <c r="E10">
@@ -900,7 +807,7 @@
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="4">
         <v>44921</v>
       </c>
       <c r="E11">
@@ -917,7 +824,7 @@
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>44922</v>
       </c>
       <c r="E12">
@@ -934,7 +841,7 @@
       <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="4">
         <v>44923</v>
       </c>
       <c r="E13">
@@ -951,7 +858,7 @@
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="4">
         <v>44924</v>
       </c>
       <c r="E14">
@@ -968,7 +875,7 @@
       <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="4">
         <v>44925</v>
       </c>
       <c r="E15">
@@ -985,7 +892,7 @@
       <c r="C16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="4">
         <v>44926</v>
       </c>
       <c r="E16">
@@ -1002,9 +909,7 @@
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="6">
-        <v>44927</v>
-      </c>
+      <c r="D17" s="4"/>
       <c r="E17">
         <v>16</v>
       </c>
@@ -1019,9 +924,7 @@
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="6">
-        <v>44928</v>
-      </c>
+      <c r="D18" s="4"/>
       <c r="E18">
         <v>17</v>
       </c>
@@ -1036,9 +939,7 @@
       <c r="C19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="6">
-        <v>44929</v>
-      </c>
+      <c r="D19" s="4"/>
       <c r="E19">
         <v>18</v>
       </c>
@@ -1053,9 +954,7 @@
       <c r="C20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="6">
-        <v>44930</v>
-      </c>
+      <c r="D20" s="4"/>
       <c r="E20">
         <v>19</v>
       </c>
@@ -1070,9 +969,7 @@
       <c r="C21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="6">
-        <v>44931</v>
-      </c>
+      <c r="D21" s="4"/>
       <c r="E21">
         <v>20</v>
       </c>
@@ -1087,12 +984,7 @@
       <c r="C22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="6">
-        <v>44932</v>
-      </c>
-      <c r="E22">
-        <v>21</v>
-      </c>
+      <c r="D22" s="4"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
@@ -1104,12 +996,7 @@
       <c r="C23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="6">
-        <v>44933</v>
-      </c>
-      <c r="E23">
-        <v>22</v>
-      </c>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
@@ -1121,12 +1008,7 @@
       <c r="C24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="6">
-        <v>44934</v>
-      </c>
-      <c r="E24">
-        <v>23</v>
-      </c>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
@@ -1138,12 +1020,7 @@
       <c r="C25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="6">
-        <v>44935</v>
-      </c>
-      <c r="E25">
-        <v>24</v>
-      </c>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
@@ -1155,12 +1032,7 @@
       <c r="C26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="6">
-        <v>44936</v>
-      </c>
-      <c r="E26">
-        <v>25</v>
-      </c>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
@@ -1172,12 +1044,7 @@
       <c r="C27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D27" s="6">
-        <v>44937</v>
-      </c>
-      <c r="E27">
-        <v>26</v>
-      </c>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
@@ -1189,12 +1056,7 @@
       <c r="C28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="6">
-        <v>44938</v>
-      </c>
-      <c r="E28">
-        <v>27</v>
-      </c>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
@@ -1206,12 +1068,7 @@
       <c r="C29" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="6">
-        <v>44939</v>
-      </c>
-      <c r="E29">
-        <v>28</v>
-      </c>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
@@ -1223,12 +1080,7 @@
       <c r="C30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="6">
-        <v>44940</v>
-      </c>
-      <c r="E30">
-        <v>29</v>
-      </c>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
@@ -1240,12 +1092,7 @@
       <c r="C31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="6">
-        <v>44941</v>
-      </c>
-      <c r="E31">
-        <v>30</v>
-      </c>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -1257,14 +1104,9 @@
       <c r="C32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="6">
-        <v>44942</v>
-      </c>
-      <c r="E32">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1274,14 +1116,9 @@
       <c r="C33" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="6">
-        <v>44943</v>
-      </c>
-      <c r="E33">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D33" s="4"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1291,14 +1128,9 @@
       <c r="C34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="6">
-        <v>44944</v>
-      </c>
-      <c r="E34">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1308,14 +1140,9 @@
       <c r="C35" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="6">
-        <v>44945</v>
-      </c>
-      <c r="E35">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="D35" s="4"/>
+    </row>
+    <row r="36" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1325,14 +1152,9 @@
       <c r="C36" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="6">
-        <v>44946</v>
-      </c>
-      <c r="E36">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D36" s="4"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1342,14 +1164,9 @@
       <c r="C37" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="6">
-        <v>44947</v>
-      </c>
-      <c r="E37">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D37" s="4"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1359,14 +1176,9 @@
       <c r="C38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D38" s="6">
-        <v>44948</v>
-      </c>
-      <c r="E38">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D38" s="4"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1376,14 +1188,9 @@
       <c r="C39" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D39" s="6">
-        <v>44949</v>
-      </c>
-      <c r="E39">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D39" s="4"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1393,14 +1200,9 @@
       <c r="C40" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D40" s="6">
-        <v>44950</v>
-      </c>
-      <c r="E40">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D40" s="4"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1410,539 +1212,162 @@
       <c r="C41" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="6">
-        <v>44951</v>
-      </c>
-      <c r="E41">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D42" s="6">
-        <v>44952</v>
-      </c>
-      <c r="E42">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D43" s="6">
-        <v>44953</v>
-      </c>
-      <c r="E43">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D44" s="6">
-        <v>44954</v>
-      </c>
-      <c r="E44">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45" s="6">
-        <v>44955</v>
-      </c>
-      <c r="E45">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D46" s="6">
-        <v>44956</v>
-      </c>
-      <c r="E46">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D47" s="6">
-        <v>44957</v>
-      </c>
-      <c r="E47">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D48" s="6">
-        <v>44958</v>
-      </c>
-      <c r="E48">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D49" s="6">
-        <v>44959</v>
-      </c>
-      <c r="E49">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D50" s="6">
-        <v>44960</v>
-      </c>
-      <c r="E50">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D51" s="6">
-        <v>44961</v>
-      </c>
-      <c r="E51">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D52" s="6">
-        <v>44962</v>
-      </c>
-      <c r="E52">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D53" s="6">
-        <v>44963</v>
-      </c>
-      <c r="E53">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D54" s="6">
-        <v>44964</v>
-      </c>
-      <c r="E54">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D55" s="6">
-        <v>44965</v>
-      </c>
-      <c r="E55">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D56" s="6">
-        <v>44966</v>
-      </c>
-      <c r="E56">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D57" s="6">
-        <v>44967</v>
-      </c>
-      <c r="E57">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D58" s="6">
-        <v>44968</v>
-      </c>
-      <c r="E58">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D59" s="6">
-        <v>44969</v>
-      </c>
-      <c r="E59">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D60" s="6">
-        <v>44970</v>
-      </c>
-      <c r="E60">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D61" s="6">
-        <v>44971</v>
-      </c>
-      <c r="E61">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D62" s="6">
-        <v>44972</v>
-      </c>
-      <c r="E62">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D63" s="6">
-        <v>44973</v>
-      </c>
-      <c r="E63">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D64" s="6">
-        <v>44974</v>
-      </c>
-      <c r="E64">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D65" s="6">
-        <v>44975</v>
-      </c>
-      <c r="E65">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D66" s="6">
-        <v>44976</v>
-      </c>
-      <c r="E66">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D67" s="6">
-        <v>44977</v>
-      </c>
-      <c r="E67">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D68" s="6">
-        <v>44978</v>
-      </c>
-      <c r="E68">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D69" s="6">
-        <v>44979</v>
-      </c>
-      <c r="E69">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D70" s="6">
-        <v>44980</v>
-      </c>
-      <c r="E70">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D71" s="6">
-        <v>44981</v>
-      </c>
-      <c r="E71">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D72" s="6">
-        <v>44982</v>
-      </c>
-      <c r="E72">
-        <v>71</v>
-      </c>
+      <c r="D41" s="4"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="4"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="4"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="4"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="4"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="4"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="4"/>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="4"/>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="4"/>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="4"/>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="4"/>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="4"/>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="4"/>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="4"/>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="4"/>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="4"/>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="4"/>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="4"/>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="4"/>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="4"/>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="4"/>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="4"/>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="4"/>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="4"/>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="4"/>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="4"/>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="4"/>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="4"/>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="4"/>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="4"/>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
